--- a/sheets/S08A22P223.xlsx
+++ b/sheets/S08A22P223.xlsx
@@ -1288,7 +1288,7 @@
     <t>IOX1312784</t>
   </si>
   <si>
-    <t>HR/03/15/0324453</t>
+    <t>HR/03/15/0345108</t>
   </si>
   <si>
     <t>Bala Devi</t>
@@ -4219,7 +4219,7 @@
     <t>HR/03/15/0345281</t>
   </si>
   <si>
-    <t>HR/03/15/0345108</t>
+    <t>HR/03/15/0346108</t>
   </si>
   <si>
     <t>Hava Singh</t>
